--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956006</v>
       </c>
       <c r="B2" t="n">
-        <v>43318</v>
+        <v>43331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956006</v>
       </c>
       <c r="B2" t="n">
-        <v>43331</v>
+        <v>43333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956006</v>
       </c>
       <c r="B2" t="n">
-        <v>43333</v>
+        <v>43343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136956006</v>
       </c>
       <c r="B2" t="n">
-        <v>43343</v>
+        <v>43344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 10476-2022 artfynd.xlsx
+++ b/artfynd/A 10476-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136956013</v>
       </c>
       <c r="B3" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
